--- a/artfynd/A 33811-2026 artfynd.xlsx
+++ b/artfynd/A 33811-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136107744</v>
       </c>
       <c r="B3" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136108015</v>
       </c>
       <c r="B4" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136108448</v>
       </c>
       <c r="B5" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>136108610</v>
       </c>
       <c r="B6" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136109735</v>
       </c>
       <c r="B7" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33811-2026 artfynd.xlsx
+++ b/artfynd/A 33811-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136107744</v>
       </c>
       <c r="B3" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136108015</v>
       </c>
       <c r="B4" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136108448</v>
       </c>
       <c r="B5" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>136108610</v>
       </c>
       <c r="B6" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136109735</v>
       </c>
       <c r="B7" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33811-2026 artfynd.xlsx
+++ b/artfynd/A 33811-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136108694</v>
       </c>
       <c r="B2" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136107744</v>
       </c>
       <c r="B3" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>136108015</v>
       </c>
       <c r="B4" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>136108448</v>
       </c>
       <c r="B5" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>136108610</v>
       </c>
       <c r="B6" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1299,7 +1299,7 @@
         <v>136109735</v>
       </c>
       <c r="B7" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
